--- a/Assets/Resource/Magic/Magic.xlsx
+++ b/Assets/Resource/Magic/Magic.xlsx
@@ -125,13 +125,13 @@
     <t>6</t>
   </si>
   <si>
-    <t>摸到之后必须立即使用（无论主动被动），无法被弃置或打断。使用后摸一张牌，并且使场上所有的玩家减少一点生命值，此生命值减少效果无视死亡感应。（龙息无法成为特殊法术模仿或坟场的目标）</t>
+    <t>摸到之后必须立即使用（无论主动被动）,使用后摸一张牌，并且场上所有的玩家减少一点生命值，此生命值减少无视死亡感应。</t>
   </si>
   <si>
     <t>变幻法球</t>
   </si>
   <si>
-    <t>？</t>
+    <t>?</t>
   </si>
   <si>
     <t>主动使用，且当具有元素法术技能时可以使用，否则无法使用。使用前你需要选择你所拥有的元素法输入技能中的一个，法球将视为该元素的基础法术。</t>

--- a/Assets/Resource/Magic/Magic.xlsx
+++ b/Assets/Resource/Magic/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>基础水法术</t>
   </si>
@@ -62,7 +62,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>13</t>
+    <t>12</t>
   </si>
   <si>
     <t>主动使用，造成一点万能属性伤害。</t>
@@ -71,16 +71,19 @@
     <t>被动使用，阻挡一点任意属性伤害。</t>
   </si>
   <si>
-    <t>万能盾</t>
-  </si>
-  <si>
-    <t>被动使用，抵挡2点任意属性的伤害。</t>
+    <t>迷你盾</t>
+  </si>
+  <si>
+    <t>星之盾</t>
+  </si>
+  <si>
+    <t>被动使用，抵挡3点任意属性的伤害。</t>
   </si>
   <si>
     <t>万能斩</t>
   </si>
   <si>
-    <t>主动使用，无万能属性伤害。若对方死亡感应触发，伤害值+2；若对方生命值小于等于3，伤害值+1。</t>
+    <t>主动使用，造成一点万能属性伤害。若对方死亡感应触发，伤害值+1。</t>
   </si>
   <si>
     <t>光芒</t>
@@ -89,7 +92,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>9</t>
+    <t>7</t>
   </si>
   <si>
     <t>主动使用，回复一点法力值，摸一张牌。</t>
@@ -134,7 +137,7 @@
     <t>?</t>
   </si>
   <si>
-    <t>主动使用，且当具有元素法术技能时可以使用，否则无法使用。使用前你需要选择你所拥有的元素法输入技能中的一个，法球将视为该元素的基础法术。</t>
+    <t>主动使用，且具有元素法术技能时可以使用，否则无法使用。使用前你需要选择你所拥有的元素法输入技能中的一个，法球将视为该元素的基础法术。</t>
   </si>
   <si>
     <t>模仿</t>
@@ -146,7 +149,7 @@
     <t>坟场</t>
   </si>
   <si>
-    <t>被动使用，当某一名玩家使用的手牌结算完效果进入弃牌堆时，你可以立即将这张牌打出，然后获得刚进入弃牌堆的一张牌。</t>
+    <t>被动使用，当其他玩家使用的手牌结算完效果进入弃牌堆时，你可以立即将这张牌打出，然后获得刚进入弃牌堆的一张牌。</t>
   </si>
   <si>
     <t>巫术响指</t>
@@ -210,7 +213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -316,231 +319,248 @@
         <v>1</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="0" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="0" t="s">
         <v>23</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="0" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="0" t="s">
         <v>29</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="0" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="0" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="0" t="s">
         <v>35</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="0" t="s">
         <v>38</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="0" t="s">
         <v>45</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="0" t="s">
         <v>47</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="0" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="0" t="s">
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
         <v>50</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Magic/Magic.xlsx
+++ b/Assets/Resource/Magic/Magic.xlsx
@@ -83,7 +83,7 @@
     <t>万能斩</t>
   </si>
   <si>
-    <t>主动使用，造成一点万能属性伤害。若对方死亡感应触发，伤害值+1。</t>
+    <t>主动使用，造成一点万能属性伤害。若对方死亡感应触发，则额外附带一点万能属性伤害。</t>
   </si>
   <si>
     <t>光芒</t>
@@ -128,7 +128,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>摸到之后必须立即使用（无论主动被动）,使用后摸一张牌，并且场上所有的玩家减少一点生命值，此生命值减少无视死亡感应。</t>
+    <t>摸到之后必须立即使用（无论主动被动），使用后摸一张牌，并且使所有玩家减少一点生命值，此生命值减少无视死亡感应。（无法被打断，无法成为特殊法术模仿或坟场的目标）</t>
   </si>
   <si>
     <t>变幻法球</t>
@@ -155,7 +155,7 @@
     <t>巫术响指</t>
   </si>
   <si>
-    <t>被动使用，打断目标的一张元素法术牌。</t>
+    <t>被动使用，打断目标的一张法术牌。</t>
   </si>
   <si>
     <t>愈合</t>
